--- a/Data/database_survival_sports_reporting.xlsx
+++ b/Data/database_survival_sports_reporting.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\La meva unitat\Docencia\TFM TFG\ACTUALS\TFM Survival esport\Github\survival-sports-reporting\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C291C4B-FD3C-47F6-A913-2131D58E4AA3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098F0A3F-EC69-4F04-9FD0-68A00213F990}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D447BC84-D6E7-4F8B-A5B7-777333882F3A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Articles" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Articles!$B$1:$BK$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Articles!$A$1:$BM$139</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7921" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8199" uniqueCount="881">
   <si>
     <t>Title</t>
   </si>
@@ -2539,13 +2539,145 @@
   </si>
   <si>
     <t>Censoring type</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>Reason Cat</t>
+  </si>
+  <si>
+    <t>ambigious what is association?</t>
+  </si>
+  <si>
+    <t>Ambigious</t>
+  </si>
+  <si>
+    <t>what is the reason for the evaluation?</t>
+  </si>
+  <si>
+    <t>not specific towards time-to-event</t>
+  </si>
+  <si>
+    <t>Not specific</t>
+  </si>
+  <si>
+    <t>what is the reason for the investigation?</t>
+  </si>
+  <si>
+    <t>what is the reason for the comparison?</t>
+  </si>
+  <si>
+    <t>ambigious what is association? who is the reference group?</t>
+  </si>
+  <si>
+    <t>why is the survival analysis performed?</t>
+  </si>
+  <si>
+    <t>what are the "two groups"?</t>
+  </si>
+  <si>
+    <t>Control group</t>
+  </si>
+  <si>
+    <t>what is prognostic factors?</t>
+  </si>
+  <si>
+    <t>Who is the reference group? Controls?</t>
+  </si>
+  <si>
+    <t>what is the reason for the correlation?</t>
+  </si>
+  <si>
+    <t>what is the reason for the association?</t>
+  </si>
+  <si>
+    <t>unclear what is meant by "the outcome"</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>what is meant by "evaluate the outcome"?</t>
+  </si>
+  <si>
+    <t>what is a risk factor?</t>
+  </si>
+  <si>
+    <t>what is the reason for investigating such "relationships"?</t>
+  </si>
+  <si>
+    <t>what is the reason for examining such association?</t>
+  </si>
+  <si>
+    <t>what is "the outcome"</t>
+  </si>
+  <si>
+    <t>what is the reason for examining such "interplay"?</t>
+  </si>
+  <si>
+    <t>what is the reason for the comparision?</t>
+  </si>
+  <si>
+    <t>what is the outcome?</t>
+  </si>
+  <si>
+    <t>it is the incidence rate? Follow-up time missing</t>
+  </si>
+  <si>
+    <t>what is the outcome? what is the reason for the assessment?</t>
+  </si>
+  <si>
+    <t>what is the reference? control group?</t>
+  </si>
+  <si>
+    <t>what is the reason for the analysis?</t>
+  </si>
+  <si>
+    <t>prediction vs causality</t>
+  </si>
+  <si>
+    <t>Prediction vs. Causality</t>
+  </si>
+  <si>
+    <t>why make such comparison?</t>
+  </si>
+  <si>
+    <t>unclear, unspecific to survival analysis</t>
+  </si>
+  <si>
+    <t>Unclear</t>
+  </si>
+  <si>
+    <t>unclear</t>
+  </si>
+  <si>
+    <t>target group missing</t>
+  </si>
+  <si>
+    <t>Survival of...?</t>
+  </si>
+  <si>
+    <t>what is functional outcome?</t>
+  </si>
+  <si>
+    <t>what is clinical outcomes?</t>
+  </si>
+  <si>
+    <t>no outcome mentioned</t>
+  </si>
+  <si>
+    <t>what is an association?</t>
+  </si>
+  <si>
+    <t>Party</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2557,6 +2689,23 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2582,101 +2731,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2986,7 +3053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E50B9A0-3402-48C2-AB95-246022EE52A7}">
-  <dimension ref="A1:BK139"/>
+  <dimension ref="A1:BM139"/>
   <sheetFormatPr defaultColWidth="112.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -3032,10 +3099,12 @@
     <col min="61" max="61" width="17.140625" style="1" customWidth="1"/>
     <col min="62" max="62" width="18.42578125" style="1" customWidth="1"/>
     <col min="63" max="63" width="18.85546875" style="1" customWidth="1"/>
-    <col min="64" max="16384" width="112.42578125" style="1"/>
+    <col min="64" max="64" width="56.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="56.28515625" style="6" customWidth="1"/>
+    <col min="66" max="16384" width="112.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" s="2" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" s="2" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>824</v>
       </c>
@@ -3225,8 +3294,14 @@
       <c r="BK1" s="2" t="s">
         <v>788</v>
       </c>
+      <c r="BL1" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="BM1" s="4" t="s">
+        <v>838</v>
+      </c>
     </row>
-    <row r="2" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3362,7 +3437,7 @@
         <v>394</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT2" s="1" t="s">
         <v>377</v>
@@ -3415,8 +3490,14 @@
       <c r="BK2" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL2" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="BM2" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="3" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3552,7 +3633,7 @@
         <v>394</v>
       </c>
       <c r="AS3" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT3" s="1" t="s">
         <v>377</v>
@@ -3605,8 +3686,14 @@
       <c r="BK3" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL3" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="BM3" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="4" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3795,8 +3882,14 @@
       <c r="BK4" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL4" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM4" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="5" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3932,7 +4025,7 @@
         <v>394</v>
       </c>
       <c r="AS5" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT5" s="1" t="s">
         <v>377</v>
@@ -3985,8 +4078,14 @@
       <c r="BK5" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL5" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="BM5" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="6" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -4122,7 +4221,7 @@
         <v>394</v>
       </c>
       <c r="AS6" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AT6" s="1" t="s">
         <v>377</v>
@@ -4175,8 +4274,14 @@
       <c r="BK6" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL6" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="BM6" s="5" t="s">
+        <v>843</v>
+      </c>
     </row>
-    <row r="7" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -4365,8 +4470,14 @@
       <c r="BK7" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL7" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM7" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="8" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -4502,7 +4613,7 @@
         <v>394</v>
       </c>
       <c r="AS8" s="1" t="s">
-        <v>377</v>
+        <v>880</v>
       </c>
       <c r="AT8" s="1" t="s">
         <v>377</v>
@@ -4555,8 +4666,14 @@
       <c r="BK8" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL8" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="BM8" s="5" t="s">
+        <v>843</v>
+      </c>
     </row>
-    <row r="9" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -4745,8 +4862,14 @@
       <c r="BK9" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL9" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM9" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="10" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -4935,8 +5058,14 @@
       <c r="BK10" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL10" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM10" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="11" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -5072,7 +5201,7 @@
         <v>394</v>
       </c>
       <c r="AS11" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AT11" s="1" t="s">
         <v>377</v>
@@ -5125,8 +5254,14 @@
       <c r="BK11" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL11" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="BM11" s="5" t="s">
+        <v>843</v>
+      </c>
     </row>
-    <row r="12" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -5262,7 +5397,7 @@
         <v>394</v>
       </c>
       <c r="AS12" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AT12" s="1" t="s">
         <v>377</v>
@@ -5315,8 +5450,14 @@
       <c r="BK12" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL12" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="BM12" s="5" t="s">
+        <v>843</v>
+      </c>
     </row>
-    <row r="13" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -5452,7 +5593,7 @@
         <v>394</v>
       </c>
       <c r="AS13" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT13" s="1" t="s">
         <v>377</v>
@@ -5505,8 +5646,14 @@
       <c r="BK13" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL13" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="BM13" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="14" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -5642,7 +5789,7 @@
         <v>394</v>
       </c>
       <c r="AS14" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT14" s="1" t="s">
         <v>377</v>
@@ -5695,8 +5842,14 @@
       <c r="BK14" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL14" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="BM14" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="15" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -5832,7 +5985,7 @@
         <v>394</v>
       </c>
       <c r="AS15" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT15" s="1" t="s">
         <v>377</v>
@@ -5885,8 +6038,14 @@
       <c r="BK15" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL15" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="BM15" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="16" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -6022,7 +6181,7 @@
         <v>394</v>
       </c>
       <c r="AS16" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT16" s="1" t="s">
         <v>377</v>
@@ -6075,8 +6234,14 @@
       <c r="BK16" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL16" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="BM16" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="17" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -6265,8 +6430,14 @@
       <c r="BK17" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL17" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM17" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="18" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -6402,7 +6573,7 @@
         <v>394</v>
       </c>
       <c r="AS18" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT18" s="1" t="s">
         <v>377</v>
@@ -6455,8 +6626,14 @@
       <c r="BK18" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL18" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="BM18" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="19" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -6592,7 +6769,7 @@
         <v>394</v>
       </c>
       <c r="AS19" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT19" s="1" t="s">
         <v>377</v>
@@ -6645,8 +6822,14 @@
       <c r="BK19" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL19" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="BM19" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="20" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -6782,7 +6965,7 @@
         <v>394</v>
       </c>
       <c r="AS20" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT20" s="1" t="s">
         <v>377</v>
@@ -6835,8 +7018,14 @@
       <c r="BK20" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL20" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="BM20" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="21" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -7025,8 +7214,14 @@
       <c r="BK21" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL21" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM21" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="22" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -7162,7 +7357,7 @@
         <v>394</v>
       </c>
       <c r="AS22" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT22" s="1" t="s">
         <v>377</v>
@@ -7215,8 +7410,14 @@
       <c r="BK22" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL22" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="BM22" s="5" t="s">
+        <v>849</v>
+      </c>
     </row>
-    <row r="23" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -7405,8 +7606,14 @@
       <c r="BK23" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL23" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM23" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="24" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -7542,7 +7749,7 @@
         <v>394</v>
       </c>
       <c r="AS24" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT24" s="1" t="s">
         <v>377</v>
@@ -7595,8 +7802,14 @@
       <c r="BK24" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL24" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="BM24" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="25" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -7785,8 +7998,14 @@
       <c r="BK25" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL25" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM25" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="26" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -7922,7 +8141,7 @@
         <v>394</v>
       </c>
       <c r="AS26" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT26" s="1" t="s">
         <v>377</v>
@@ -7975,8 +8194,14 @@
       <c r="BK26" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL26" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="BM26" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="27" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -8112,7 +8337,7 @@
         <v>394</v>
       </c>
       <c r="AS27" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT27" s="1" t="s">
         <v>377</v>
@@ -8165,8 +8390,14 @@
       <c r="BK27" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL27" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="BM27" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="28" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -8355,8 +8586,14 @@
       <c r="BK28" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL28" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM28" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="29" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -8492,7 +8729,7 @@
         <v>394</v>
       </c>
       <c r="AS29" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT29" s="1" t="s">
         <v>377</v>
@@ -8545,8 +8782,14 @@
       <c r="BK29" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL29" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="BM29" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="30" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -8682,7 +8925,7 @@
         <v>394</v>
       </c>
       <c r="AS30" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT30" s="1" t="s">
         <v>377</v>
@@ -8735,8 +8978,14 @@
       <c r="BK30" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL30" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="BM30" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="31" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -8925,8 +9174,14 @@
       <c r="BK31" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL31" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM31" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="32" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -9062,7 +9317,7 @@
         <v>394</v>
       </c>
       <c r="AS32" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT32" s="1" t="s">
         <v>377</v>
@@ -9115,8 +9370,14 @@
       <c r="BK32" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL32" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="BM32" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="33" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -9252,7 +9513,7 @@
         <v>394</v>
       </c>
       <c r="AS33" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AT33" s="1" t="s">
         <v>377</v>
@@ -9305,8 +9566,14 @@
       <c r="BK33" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL33" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="BM33" s="5" t="s">
+        <v>843</v>
+      </c>
     </row>
-    <row r="34" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -9495,8 +9762,14 @@
       <c r="BK34" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL34" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM34" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="35" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -9632,7 +9905,7 @@
         <v>394</v>
       </c>
       <c r="AS35" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT35" s="1" t="s">
         <v>377</v>
@@ -9685,8 +9958,14 @@
       <c r="BK35" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL35" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="BM35" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="36" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -9822,7 +10101,7 @@
         <v>394</v>
       </c>
       <c r="AS36" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT36" s="1" t="s">
         <v>377</v>
@@ -9875,8 +10154,14 @@
       <c r="BK36" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL36" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="BM36" s="5" t="s">
+        <v>849</v>
+      </c>
     </row>
-    <row r="37" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -10065,8 +10350,14 @@
       <c r="BK37" s="1" t="s">
         <v>377</v>
       </c>
+      <c r="BL37" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM37" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="38" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -10255,8 +10546,14 @@
       <c r="BK38" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL38" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM38" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="39" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -10392,7 +10689,7 @@
         <v>394</v>
       </c>
       <c r="AS39" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AT39" s="1" t="s">
         <v>377</v>
@@ -10445,8 +10742,14 @@
       <c r="BK39" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL39" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="BM39" s="5" t="s">
+        <v>843</v>
+      </c>
     </row>
-    <row r="40" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -10582,7 +10885,7 @@
         <v>394</v>
       </c>
       <c r="AS40" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT40" s="1" t="s">
         <v>377</v>
@@ -10635,8 +10938,14 @@
       <c r="BK40" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL40" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="BM40" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="41" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -10772,7 +11081,7 @@
         <v>394</v>
       </c>
       <c r="AS41" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT41" s="1" t="s">
         <v>377</v>
@@ -10825,8 +11134,14 @@
       <c r="BK41" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL41" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="BM41" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="42" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -10962,7 +11277,7 @@
         <v>394</v>
       </c>
       <c r="AS42" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT42" s="1" t="s">
         <v>377</v>
@@ -11015,8 +11330,14 @@
       <c r="BK42" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL42" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="BM42" s="5" t="s">
+        <v>849</v>
+      </c>
     </row>
-    <row r="43" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -11152,7 +11473,7 @@
         <v>394</v>
       </c>
       <c r="AS43" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT43" s="1" t="s">
         <v>377</v>
@@ -11205,8 +11526,14 @@
       <c r="BK43" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL43" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="BM43" s="5" t="s">
+        <v>849</v>
+      </c>
     </row>
-    <row r="44" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -11342,7 +11669,7 @@
         <v>394</v>
       </c>
       <c r="AS44" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT44" s="1" t="s">
         <v>377</v>
@@ -11395,8 +11722,14 @@
       <c r="BK44" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL44" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="BM44" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="45" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -11532,7 +11865,7 @@
         <v>394</v>
       </c>
       <c r="AS45" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT45" s="1" t="s">
         <v>377</v>
@@ -11585,8 +11918,14 @@
       <c r="BK45" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL45" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="BM45" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="46" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -11775,8 +12114,14 @@
       <c r="BK46" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL46" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM46" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="47" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -11912,7 +12257,7 @@
         <v>394</v>
       </c>
       <c r="AS47" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT47" s="1" t="s">
         <v>377</v>
@@ -11965,8 +12310,14 @@
       <c r="BK47" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL47" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="BM47" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="48" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -12102,7 +12453,7 @@
         <v>394</v>
       </c>
       <c r="AS48" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT48" s="1" t="s">
         <v>377</v>
@@ -12155,8 +12506,14 @@
       <c r="BK48" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL48" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="BM48" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="49" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -12292,7 +12649,7 @@
         <v>394</v>
       </c>
       <c r="AS49" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT49" s="1" t="s">
         <v>378</v>
@@ -12345,8 +12702,14 @@
       <c r="BK49" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL49" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="BM49" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="50" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -12535,8 +12898,14 @@
       <c r="BK50" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL50" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM50" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="51" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -12725,8 +13094,14 @@
       <c r="BK51" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL51" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM51" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="52" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -12862,7 +13237,7 @@
         <v>394</v>
       </c>
       <c r="AS52" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT52" s="1" t="s">
         <v>377</v>
@@ -12915,8 +13290,14 @@
       <c r="BK52" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL52" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="BM52" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="53" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -13105,8 +13486,14 @@
       <c r="BK53" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL53" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM53" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="54" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -13295,8 +13682,14 @@
       <c r="BK54" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL54" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM54" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="55" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -13432,7 +13825,7 @@
         <v>394</v>
       </c>
       <c r="AS55" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT55" s="1" t="s">
         <v>377</v>
@@ -13485,8 +13878,14 @@
       <c r="BK55" s="1" t="s">
         <v>377</v>
       </c>
+      <c r="BL55" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="BM55" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="56" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -13622,7 +14021,7 @@
         <v>394</v>
       </c>
       <c r="AS56" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT56" s="1" t="s">
         <v>377</v>
@@ -13675,8 +14074,14 @@
       <c r="BK56" s="1" t="s">
         <v>377</v>
       </c>
+      <c r="BL56" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="BM56" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="57" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -13812,7 +14217,7 @@
         <v>394</v>
       </c>
       <c r="AS57" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT57" s="1" t="s">
         <v>377</v>
@@ -13865,8 +14270,14 @@
       <c r="BK57" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL57" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="BM57" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="58" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -14055,8 +14466,14 @@
       <c r="BK58" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL58" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM58" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="59" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -14192,7 +14609,7 @@
         <v>394</v>
       </c>
       <c r="AS59" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT59" s="1" t="s">
         <v>377</v>
@@ -14245,8 +14662,14 @@
       <c r="BK59" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL59" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="BM59" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="60" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -14382,7 +14805,7 @@
         <v>394</v>
       </c>
       <c r="AS60" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT60" s="1" t="s">
         <v>377</v>
@@ -14435,8 +14858,14 @@
       <c r="BK60" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL60" s="5" t="s">
+        <v>861</v>
+      </c>
+      <c r="BM60" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="61" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -14569,7 +14998,7 @@
         <v>394</v>
       </c>
       <c r="AS61" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT61" s="1" t="s">
         <v>377</v>
@@ -14622,8 +15051,14 @@
       <c r="BK61" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL61" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="BM61" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="62" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -14759,7 +15194,7 @@
         <v>394</v>
       </c>
       <c r="AS62" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT62" s="1" t="s">
         <v>377</v>
@@ -14812,8 +15247,14 @@
       <c r="BK62" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL62" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="BM62" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="63" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -14949,7 +15390,7 @@
         <v>394</v>
       </c>
       <c r="AS63" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT63" s="1" t="s">
         <v>377</v>
@@ -15002,8 +15443,14 @@
       <c r="BK63" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL63" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="BM63" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="64" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -15192,8 +15639,14 @@
       <c r="BK64" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL64" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM64" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="65" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -15382,8 +15835,14 @@
       <c r="BK65" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL65" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM65" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="66" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -15519,7 +15978,7 @@
         <v>394</v>
       </c>
       <c r="AS66" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT66" s="1" t="s">
         <v>377</v>
@@ -15572,8 +16031,14 @@
       <c r="BK66" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL66" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="BM66" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="67" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -15709,7 +16174,7 @@
         <v>394</v>
       </c>
       <c r="AS67" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT67" s="1" t="s">
         <v>378</v>
@@ -15762,8 +16227,14 @@
       <c r="BK67" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL67" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="BM67" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="68" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -15952,8 +16423,14 @@
       <c r="BK68" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL68" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM68" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="69" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -16089,7 +16566,7 @@
         <v>394</v>
       </c>
       <c r="AS69" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT69" s="1" t="s">
         <v>377</v>
@@ -16142,8 +16619,14 @@
       <c r="BK69" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL69" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="BM69" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="70" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -16279,7 +16762,7 @@
         <v>394</v>
       </c>
       <c r="AS70" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT70" s="1" t="s">
         <v>377</v>
@@ -16332,8 +16815,14 @@
       <c r="BK70" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL70" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="BM70" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="71" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -16522,8 +17011,14 @@
       <c r="BK71" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL71" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM71" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="72" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -16659,7 +17154,7 @@
         <v>394</v>
       </c>
       <c r="AS72" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT72" s="1" t="s">
         <v>377</v>
@@ -16712,8 +17207,14 @@
       <c r="BK72" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL72" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="BM72" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="73" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -16849,7 +17350,7 @@
         <v>394</v>
       </c>
       <c r="AS73" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT73" s="1" t="s">
         <v>377</v>
@@ -16902,8 +17403,14 @@
       <c r="BK73" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL73" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="BM73" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="74" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -17039,7 +17546,7 @@
         <v>394</v>
       </c>
       <c r="AS74" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT74" s="1" t="s">
         <v>377</v>
@@ -17092,8 +17599,14 @@
       <c r="BK74" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL74" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="BM74" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="75" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -17229,7 +17742,7 @@
         <v>394</v>
       </c>
       <c r="AS75" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT75" s="1" t="s">
         <v>377</v>
@@ -17282,8 +17795,14 @@
       <c r="BK75" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL75" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="BM75" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="76" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -17419,7 +17938,7 @@
         <v>394</v>
       </c>
       <c r="AS76" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT76" s="1" t="s">
         <v>377</v>
@@ -17472,8 +17991,14 @@
       <c r="BK76" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL76" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="BM76" s="5" t="s">
+        <v>849</v>
+      </c>
     </row>
-    <row r="77" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -17609,7 +18134,7 @@
         <v>394</v>
       </c>
       <c r="AS77" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT77" s="1" t="s">
         <v>377</v>
@@ -17662,8 +18187,14 @@
       <c r="BK77" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL77" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="BM77" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="78" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -17799,7 +18330,7 @@
         <v>394</v>
       </c>
       <c r="AS78" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT78" s="1" t="s">
         <v>377</v>
@@ -17852,8 +18383,14 @@
       <c r="BK78" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL78" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="BM78" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="79" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -17989,7 +18526,7 @@
         <v>394</v>
       </c>
       <c r="AS79" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT79" s="1" t="s">
         <v>377</v>
@@ -18042,8 +18579,14 @@
       <c r="BK79" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL79" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="BM79" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="80" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -18179,7 +18722,7 @@
         <v>394</v>
       </c>
       <c r="AS80" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT80" s="1" t="s">
         <v>377</v>
@@ -18232,8 +18775,14 @@
       <c r="BK80" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL80" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="BM80" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="81" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -18369,7 +18918,7 @@
         <v>394</v>
       </c>
       <c r="AS81" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT81" s="1" t="s">
         <v>377</v>
@@ -18422,8 +18971,14 @@
       <c r="BK81" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL81" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM81" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="82" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -18559,7 +19114,7 @@
         <v>394</v>
       </c>
       <c r="AS82" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT82" s="1" t="s">
         <v>377</v>
@@ -18612,8 +19167,14 @@
       <c r="BK82" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL82" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="BM82" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="83" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -18749,7 +19310,7 @@
         <v>394</v>
       </c>
       <c r="AS83" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT83" s="1" t="s">
         <v>377</v>
@@ -18802,8 +19363,14 @@
       <c r="BK83" s="1" t="s">
         <v>377</v>
       </c>
+      <c r="BL83" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="BM83" s="5" t="s">
+        <v>849</v>
+      </c>
     </row>
-    <row r="84" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -18939,7 +19506,7 @@
         <v>394</v>
       </c>
       <c r="AS84" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT84" s="1" t="s">
         <v>377</v>
@@ -18992,8 +19559,14 @@
       <c r="BK84" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL84" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="BM84" s="5" t="s">
+        <v>837</v>
+      </c>
     </row>
-    <row r="85" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -19129,7 +19702,7 @@
         <v>394</v>
       </c>
       <c r="AS85" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT85" s="1" t="s">
         <v>377</v>
@@ -19182,8 +19755,14 @@
       <c r="BK85" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL85" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="BM85" s="5" t="s">
+        <v>872</v>
+      </c>
     </row>
-    <row r="86" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -19372,8 +19951,14 @@
       <c r="BK86" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL86" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM86" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="87" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -19509,7 +20094,7 @@
         <v>394</v>
       </c>
       <c r="AS87" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT87" s="1" t="s">
         <v>377</v>
@@ -19562,8 +20147,14 @@
       <c r="BK87" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL87" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="BM87" s="5" t="s">
+        <v>872</v>
+      </c>
     </row>
-    <row r="88" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -19699,7 +20290,7 @@
         <v>394</v>
       </c>
       <c r="AS88" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT88" s="1" t="s">
         <v>377</v>
@@ -19752,8 +20343,14 @@
       <c r="BK88" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL88" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="BM88" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="89" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -19942,8 +20539,14 @@
       <c r="BK89" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL89" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM89" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="90" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -20132,8 +20735,14 @@
       <c r="BK90" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL90" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM90" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="91" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -20322,8 +20931,14 @@
       <c r="BK91" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL91" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM91" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="92" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -20459,7 +21074,7 @@
         <v>394</v>
       </c>
       <c r="AS92" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT92" s="1" t="s">
         <v>377</v>
@@ -20512,8 +21127,14 @@
       <c r="BK92" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL92" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM92" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="93" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -20702,8 +21323,14 @@
       <c r="BK93" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL93" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM93" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="94" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -20892,8 +21519,14 @@
       <c r="BK94" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL94" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM94" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="95" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -21029,7 +21662,7 @@
         <v>394</v>
       </c>
       <c r="AS95" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT95" s="1" t="s">
         <v>377</v>
@@ -21082,8 +21715,14 @@
       <c r="BK95" s="1" t="s">
         <v>377</v>
       </c>
+      <c r="BL95" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="BM95" s="5" t="s">
+        <v>849</v>
+      </c>
     </row>
-    <row r="96" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -21272,8 +21911,14 @@
       <c r="BK96" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL96" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM96" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="97" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -21409,7 +22054,7 @@
         <v>394</v>
       </c>
       <c r="AS97" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT97" s="1" t="s">
         <v>377</v>
@@ -21462,8 +22107,14 @@
       <c r="BK97" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL97" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM97" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="98" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -21599,7 +22250,7 @@
         <v>394</v>
       </c>
       <c r="AS98" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT98" s="1" t="s">
         <v>377</v>
@@ -21652,8 +22303,14 @@
       <c r="BK98" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL98" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="BM98" s="5" t="s">
+        <v>849</v>
+      </c>
     </row>
-    <row r="99" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -21789,7 +22446,7 @@
         <v>394</v>
       </c>
       <c r="AS99" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT99" s="1" t="s">
         <v>377</v>
@@ -21842,8 +22499,14 @@
       <c r="BK99" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL99" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM99" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="100" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -21979,7 +22642,7 @@
         <v>394</v>
       </c>
       <c r="AS100" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT100" s="1" t="s">
         <v>377</v>
@@ -22032,8 +22695,14 @@
       <c r="BK100" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL100" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM100" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="101" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -22222,8 +22891,14 @@
       <c r="BK101" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL101" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM101" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="102" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -22359,7 +23034,7 @@
         <v>394</v>
       </c>
       <c r="AS102" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT102" s="1" t="s">
         <v>377</v>
@@ -22412,8 +23087,14 @@
       <c r="BK102" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL102" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM102" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="103" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -22549,7 +23230,7 @@
         <v>394</v>
       </c>
       <c r="AS103" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT103" s="1" t="s">
         <v>377</v>
@@ -22602,8 +23283,14 @@
       <c r="BK103" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL103" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM103" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="104" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -22739,7 +23426,7 @@
         <v>394</v>
       </c>
       <c r="AS104" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT104" s="1" t="s">
         <v>377</v>
@@ -22792,8 +23479,14 @@
       <c r="BK104" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL104" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="BM104" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="105" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -22929,7 +23622,7 @@
         <v>394</v>
       </c>
       <c r="AS105" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT105" s="1" t="s">
         <v>377</v>
@@ -22982,8 +23675,14 @@
       <c r="BK105" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL105" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM105" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="106" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -23119,7 +23818,7 @@
         <v>394</v>
       </c>
       <c r="AS106" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT106" s="1" t="s">
         <v>377</v>
@@ -23172,8 +23871,14 @@
       <c r="BK106" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL106" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="BM106" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="107" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>107</v>
       </c>
@@ -23362,8 +24067,14 @@
       <c r="BK107" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL107" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM107" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="108" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>108</v>
       </c>
@@ -23552,8 +24263,14 @@
       <c r="BK108" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL108" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM108" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="109" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>109</v>
       </c>
@@ -23689,7 +24406,7 @@
         <v>394</v>
       </c>
       <c r="AS109" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT109" s="1" t="s">
         <v>378</v>
@@ -23742,8 +24459,14 @@
       <c r="BK109" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL109" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM109" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="110" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>110</v>
       </c>
@@ -23932,8 +24655,14 @@
       <c r="BK110" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL110" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM110" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="111" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>111</v>
       </c>
@@ -24069,7 +24798,7 @@
         <v>394</v>
       </c>
       <c r="AS111" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT111" s="1" t="s">
         <v>377</v>
@@ -24122,8 +24851,14 @@
       <c r="BK111" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL111" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM111" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="112" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>112</v>
       </c>
@@ -24312,8 +25047,14 @@
       <c r="BK112" s="1" t="s">
         <v>377</v>
       </c>
+      <c r="BL112" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM112" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="113" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>113</v>
       </c>
@@ -24449,7 +25190,7 @@
         <v>377</v>
       </c>
       <c r="AS113" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT113" s="1" t="s">
         <v>377</v>
@@ -24502,8 +25243,14 @@
       <c r="BK113" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL113" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="BM113" s="5" t="s">
+        <v>872</v>
+      </c>
     </row>
-    <row r="114" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>114</v>
       </c>
@@ -24639,7 +25386,7 @@
         <v>394</v>
       </c>
       <c r="AS114" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT114" s="1" t="s">
         <v>377</v>
@@ -24692,8 +25439,14 @@
       <c r="BK114" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL114" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="BM114" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="115" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>115</v>
       </c>
@@ -24882,8 +25635,14 @@
       <c r="BK115" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL115" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM115" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="116" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>116</v>
       </c>
@@ -25019,7 +25778,7 @@
         <v>394</v>
       </c>
       <c r="AS116" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT116" s="1" t="s">
         <v>377</v>
@@ -25072,8 +25831,14 @@
       <c r="BK116" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL116" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM116" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="117" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>117</v>
       </c>
@@ -25209,7 +25974,7 @@
         <v>394</v>
       </c>
       <c r="AS117" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT117" s="1" t="s">
         <v>377</v>
@@ -25262,8 +26027,14 @@
       <c r="BK117" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL117" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="BM117" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="118" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>118</v>
       </c>
@@ -25399,7 +26170,7 @@
         <v>394</v>
       </c>
       <c r="AS118" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT118" s="1" t="s">
         <v>377</v>
@@ -25452,8 +26223,14 @@
       <c r="BK118" s="1" t="s">
         <v>377</v>
       </c>
+      <c r="BL118" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="BM118" s="5" t="s">
+        <v>872</v>
+      </c>
     </row>
-    <row r="119" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>119</v>
       </c>
@@ -25589,7 +26366,7 @@
         <v>394</v>
       </c>
       <c r="AS119" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT119" s="1" t="s">
         <v>377</v>
@@ -25642,8 +26419,14 @@
       <c r="BK119" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL119" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM119" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="120" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>120</v>
       </c>
@@ -25779,7 +26562,7 @@
         <v>394</v>
       </c>
       <c r="AS120" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT120" s="1" t="s">
         <v>378</v>
@@ -25832,8 +26615,14 @@
       <c r="BK120" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL120" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="BM120" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="121" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>121</v>
       </c>
@@ -25969,7 +26758,7 @@
         <v>394</v>
       </c>
       <c r="AS121" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT121" s="1" t="s">
         <v>377</v>
@@ -26022,8 +26811,14 @@
       <c r="BK121" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL121" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="BM121" s="5" t="s">
+        <v>840</v>
+      </c>
     </row>
-    <row r="122" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>122</v>
       </c>
@@ -26159,7 +26954,7 @@
         <v>394</v>
       </c>
       <c r="AS122" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT122" s="1" t="s">
         <v>377</v>
@@ -26212,8 +27007,14 @@
       <c r="BK122" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL122" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM122" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="123" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>123</v>
       </c>
@@ -26349,7 +27150,7 @@
         <v>394</v>
       </c>
       <c r="AS123" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT123" s="1" t="s">
         <v>377</v>
@@ -26402,8 +27203,14 @@
       <c r="BK123" s="1" t="s">
         <v>377</v>
       </c>
+      <c r="BL123" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM123" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="124" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>124</v>
       </c>
@@ -26539,7 +27346,7 @@
         <v>394</v>
       </c>
       <c r="AS124" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT124" s="1" t="s">
         <v>377</v>
@@ -26592,8 +27399,14 @@
       <c r="BK124" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL124" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM124" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="125" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>125</v>
       </c>
@@ -26729,7 +27542,7 @@
         <v>394</v>
       </c>
       <c r="AS125" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT125" s="1" t="s">
         <v>377</v>
@@ -26782,8 +27595,14 @@
       <c r="BK125" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL125" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM125" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="126" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>126</v>
       </c>
@@ -26972,8 +27791,14 @@
       <c r="BK126" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL126" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM126" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="127" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>127</v>
       </c>
@@ -27162,8 +27987,14 @@
       <c r="BK127" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL127" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM127" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="128" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>128</v>
       </c>
@@ -27352,8 +28183,14 @@
       <c r="BK128" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL128" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM128" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="129" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>129</v>
       </c>
@@ -27489,7 +28326,7 @@
         <v>377</v>
       </c>
       <c r="AS129" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT129" s="1" t="s">
         <v>377</v>
@@ -27542,8 +28379,14 @@
       <c r="BK129" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL129" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="BM129" s="5" t="s">
+        <v>872</v>
+      </c>
     </row>
-    <row r="130" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>130</v>
       </c>
@@ -27679,7 +28522,7 @@
         <v>394</v>
       </c>
       <c r="AS130" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT130" s="1" t="s">
         <v>377</v>
@@ -27732,8 +28575,14 @@
       <c r="BK130" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL130" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM130" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="131" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>131</v>
       </c>
@@ -27922,8 +28771,14 @@
       <c r="BK131" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL131" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM131" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="132" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>132</v>
       </c>
@@ -28059,7 +28914,7 @@
         <v>394</v>
       </c>
       <c r="AS132" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT132" s="1" t="s">
         <v>377</v>
@@ -28112,8 +28967,14 @@
       <c r="BK132" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL132" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM132" s="5" t="s">
+        <v>869</v>
+      </c>
     </row>
-    <row r="133" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>133</v>
       </c>
@@ -28302,8 +29163,14 @@
       <c r="BK133" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL133" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM133" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="134" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>134</v>
       </c>
@@ -28492,8 +29359,14 @@
       <c r="BK134" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL134" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM134" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="135" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>135</v>
       </c>
@@ -28682,8 +29555,14 @@
       <c r="BK135" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL135" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM135" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="136" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>136</v>
       </c>
@@ -28872,8 +29751,14 @@
       <c r="BK136" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL136" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM136" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="137" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>137</v>
       </c>
@@ -29009,7 +29894,7 @@
         <v>394</v>
       </c>
       <c r="AS137" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="AT137" s="1" t="s">
         <v>377</v>
@@ -29062,8 +29947,14 @@
       <c r="BK137" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL137" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="BM137" s="5" t="s">
+        <v>855</v>
+      </c>
     </row>
-    <row r="138" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>138</v>
       </c>
@@ -29252,8 +30143,14 @@
       <c r="BK138" s="1" t="s">
         <v>377</v>
       </c>
+      <c r="BL138" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM138" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="139" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>139</v>
       </c>
@@ -29442,9 +30339,15 @@
       <c r="BK139" s="1" t="s">
         <v>394</v>
       </c>
+      <c r="BL139" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="BM139" s="5" t="s">
+        <v>825</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:BK139" xr:uid="{0E50B9A0-3402-48C2-AB95-246022EE52A7}"/>
+  <autoFilter ref="A1:BM139" xr:uid="{54D29B2E-5FCD-489E-8D04-68D9308AD475}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Data/database_survival_sports_reporting.xlsx
+++ b/Data/database_survival_sports_reporting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\La meva unitat\Docencia\TFM TFG\ACTUALS\TFM Survival esport\Github\survival-sports-reporting\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098F0A3F-EC69-4F04-9FD0-68A00213F990}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02B7B3D-3F61-4631-9789-B3832C786291}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D447BC84-D6E7-4F8B-A5B7-777333882F3A}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8199" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8199" uniqueCount="880">
   <si>
     <t>Title</t>
   </si>
@@ -2668,9 +2668,6 @@
   </si>
   <si>
     <t>what is an association?</t>
-  </si>
-  <si>
-    <t>Party</t>
   </si>
 </sst>
 </file>
@@ -4613,7 +4610,7 @@
         <v>394</v>
       </c>
       <c r="AS8" s="1" t="s">
-        <v>880</v>
+        <v>378</v>
       </c>
       <c r="AT8" s="1" t="s">
         <v>377</v>
